--- a/reports/onprem_openshift_sql_server_sizing.xlsx
+++ b/reports/onprem_openshift_sql_server_sizing.xlsx
@@ -13,6 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROD-3Yr" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROD-4Yr" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROD-5Yr" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAT" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIT" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4968,4 +4970,1358 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:O22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>UAT Environment On Premise</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>S.N.</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Services/Instances</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>Nodes</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Instance Type</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Per Node
+CPU cores</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Per Node
+RAM</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Per Node
+Storage (GB)</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>Total
+CPU cores</t>
+        </is>
+      </c>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>Total
+RAM
+(GB)</t>
+        </is>
+      </c>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>Total
+Storage
+(TB)</t>
+        </is>
+      </c>
+      <c r="M2" s="13" t="n"/>
+      <c r="N2" s="13" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="O2" s="13" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="B3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>OpenShift Cluster</t>
+        </is>
+      </c>
+      <c r="M3" s="14" t="n"/>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="14" t="n"/>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Bootstrap machine</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Memory Intensive</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>OpenShift vendor to confirm on sizing.</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" s="16" t="n">
+        <v>256</v>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="L4" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M4" s="16" t="n"/>
+      <c r="N4" s="16" t="inlineStr"/>
+      <c r="O4" s="16" t="n"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Bastion Host</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>Memory Intensive</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr"/>
+      <c r="G5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>256</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="L5" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" s="19" t="inlineStr"/>
+      <c r="O5" s="19" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Master Nodes</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Compute Intensive</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr"/>
+      <c r="G6" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>256</v>
+      </c>
+      <c r="J6" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>48</v>
+      </c>
+      <c r="L6" s="17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="16" t="inlineStr"/>
+      <c r="O6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Linux Worker Nodes (BUSINESSNEXT)</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Compute Intensive</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr"/>
+      <c r="G7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>256</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="L7" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M7" s="19" t="n"/>
+      <c r="N7" s="19" t="inlineStr"/>
+      <c r="O7" s="19" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Operational Services</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="n"/>
+      <c r="N8" s="14" t="n"/>
+      <c r="O8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Infra Nodes (Grafana &amp; Prometheus, EFK, Redis)</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>Compute Intensive</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr"/>
+      <c r="G9" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>256</v>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="L9" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="16" t="inlineStr"/>
+      <c r="O9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>NFS Storage</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="19" t="inlineStr"/>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n">
+        <v>2792</v>
+      </c>
+      <c r="J10" s="19" t="n"/>
+      <c r="K10" s="19" t="n"/>
+      <c r="L10" s="20" t="n">
+        <v>2.7265625</v>
+      </c>
+      <c r="M10" s="19" t="n"/>
+      <c r="N10" s="19" t="inlineStr"/>
+      <c r="O10" s="19" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>MSSQL Enterprise Database</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="n"/>
+      <c r="N11" s="14" t="n"/>
+      <c r="O11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Windows Nodes</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>Memory Intensive</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr"/>
+      <c r="G12" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>488</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="J12" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>488</v>
+      </c>
+      <c r="L12" s="17" t="n">
+        <v>0.29296875</v>
+      </c>
+      <c r="M12" s="16" t="n"/>
+      <c r="N12" s="16" t="inlineStr"/>
+      <c r="O12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>SQL License</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Memory Intensive</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="19" t="n"/>
+      <c r="L13" s="19" t="n"/>
+      <c r="M13" s="19" t="n"/>
+      <c r="N13" s="19" t="inlineStr"/>
+      <c r="O13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Storage: SAN</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>20K IOPS</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+      <c r="I14" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="17" t="n">
+        <v>0.48828125</v>
+      </c>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="16" t="inlineStr"/>
+      <c r="O14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="B15" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="n"/>
+      <c r="N15" s="14" t="n"/>
+      <c r="O15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>S3 Storage</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>To be consumed from main NFS storage</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>Will be based on the number of documents provided, Considering per document size per Service Request of 512KB Each.</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
+      <c r="I16" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="16" t="n"/>
+      <c r="L16" s="17" t="n">
+        <v>0.48828125</v>
+      </c>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="inlineStr"/>
+      <c r="O16" s="16" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="B17" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; Monitoring</t>
+        </is>
+      </c>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>SSL</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Provided by Bank</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="19" t="n"/>
+      <c r="M18" s="19" t="n"/>
+      <c r="N18" s="19" t="inlineStr"/>
+      <c r="O18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Image Registry</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>For Containers docker images</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr"/>
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="16" t="n"/>
+      <c r="I19" s="16" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J19" s="16" t="n"/>
+      <c r="K19" s="16" t="n"/>
+      <c r="L19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="16" t="n"/>
+      <c r="N19" s="16" t="inlineStr"/>
+      <c r="O19" s="16" t="n"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Web Application Firewall (WAF)</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="19" t="inlineStr"/>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>As per banks security policy.</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="19" t="n"/>
+      <c r="J20" s="19" t="n"/>
+      <c r="K20" s="19" t="n"/>
+      <c r="L20" s="19" t="n"/>
+      <c r="M20" s="19" t="n"/>
+      <c r="N20" s="19" t="inlineStr"/>
+      <c r="O20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Bastion Host</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="16" t="inlineStr"/>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>As per banks policy.</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>256</v>
+      </c>
+      <c r="J21" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M21" s="16" t="n"/>
+      <c r="N21" s="16" t="inlineStr"/>
+      <c r="O21" s="16" t="n"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Email Service</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Two million mails/month</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="19" t="n"/>
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="19" t="n"/>
+      <c r="L22" s="19" t="n"/>
+      <c r="M22" s="19" t="n"/>
+      <c r="N22" s="19" t="inlineStr"/>
+      <c r="O22" s="19" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="C8:O8"/>
+    <mergeCell ref="C3:O3"/>
+    <mergeCell ref="C17:O17"/>
+    <mergeCell ref="C15:O15"/>
+    <mergeCell ref="C11:O11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:O22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>SIT Environment On Premise</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>S.N.</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Services/Instances</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>Nodes</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Instance Type</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Per Node
+CPU cores</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Per Node
+RAM</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Per Node
+Storage (GB)</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>Total
+CPU cores</t>
+        </is>
+      </c>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>Total
+RAM
+(GB)</t>
+        </is>
+      </c>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>Total
+Storage
+(TB)</t>
+        </is>
+      </c>
+      <c r="M2" s="13" t="n"/>
+      <c r="N2" s="13" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="O2" s="13" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="B3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>OpenShift Cluster</t>
+        </is>
+      </c>
+      <c r="M3" s="14" t="n"/>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="14" t="n"/>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Bootstrap machine</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Memory Intensive</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>OpenShift vendor to confirm on sizing.</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" s="16" t="n">
+        <v>256</v>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="L4" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M4" s="16" t="n"/>
+      <c r="N4" s="16" t="inlineStr"/>
+      <c r="O4" s="16" t="n"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Bastion Host</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>Memory Intensive</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr"/>
+      <c r="G5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>256</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="L5" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" s="19" t="inlineStr"/>
+      <c r="O5" s="19" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Master Nodes</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Compute Intensive</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr"/>
+      <c r="G6" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>256</v>
+      </c>
+      <c r="J6" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>48</v>
+      </c>
+      <c r="L6" s="17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="16" t="inlineStr"/>
+      <c r="O6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Linux Worker Nodes (BUSINESSNEXT)</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Compute Intensive</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr"/>
+      <c r="G7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>256</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="L7" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M7" s="19" t="n"/>
+      <c r="N7" s="19" t="inlineStr"/>
+      <c r="O7" s="19" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Operational Services</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="n"/>
+      <c r="N8" s="14" t="n"/>
+      <c r="O8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Infra Nodes (Grafana &amp; Prometheus, EFK, Redis)</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>Compute Intensive</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr"/>
+      <c r="G9" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>256</v>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="L9" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="16" t="inlineStr"/>
+      <c r="O9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>NFS Storage</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="19" t="inlineStr"/>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n">
+        <v>2792</v>
+      </c>
+      <c r="J10" s="19" t="n"/>
+      <c r="K10" s="19" t="n"/>
+      <c r="L10" s="20" t="n">
+        <v>2.7265625</v>
+      </c>
+      <c r="M10" s="19" t="n"/>
+      <c r="N10" s="19" t="inlineStr"/>
+      <c r="O10" s="19" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>MSSQL Enterprise Database</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="n"/>
+      <c r="N11" s="14" t="n"/>
+      <c r="O11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Windows Nodes</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>Memory Intensive</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr"/>
+      <c r="G12" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>488</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="J12" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>488</v>
+      </c>
+      <c r="L12" s="17" t="n">
+        <v>0.29296875</v>
+      </c>
+      <c r="M12" s="16" t="n"/>
+      <c r="N12" s="16" t="inlineStr"/>
+      <c r="O12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>SQL License</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Memory Intensive</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="19" t="n"/>
+      <c r="L13" s="19" t="n"/>
+      <c r="M13" s="19" t="n"/>
+      <c r="N13" s="19" t="inlineStr"/>
+      <c r="O13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Storage: SAN</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>20K IOPS</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+      <c r="I14" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="17" t="n">
+        <v>0.48828125</v>
+      </c>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="16" t="inlineStr"/>
+      <c r="O14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="B15" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="n"/>
+      <c r="N15" s="14" t="n"/>
+      <c r="O15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>S3 Storage</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>To be consumed from main NFS storage</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>Will be based on the number of documents provided, Considering per document size per Service Request of 512KB Each.</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
+      <c r="I16" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="16" t="n"/>
+      <c r="L16" s="17" t="n">
+        <v>0.48828125</v>
+      </c>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="inlineStr"/>
+      <c r="O16" s="16" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="B17" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; Monitoring</t>
+        </is>
+      </c>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>SSL</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Provided by Bank</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="19" t="n"/>
+      <c r="M18" s="19" t="n"/>
+      <c r="N18" s="19" t="inlineStr"/>
+      <c r="O18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Image Registry</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>For Containers docker images</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr"/>
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="16" t="n"/>
+      <c r="I19" s="16" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J19" s="16" t="n"/>
+      <c r="K19" s="16" t="n"/>
+      <c r="L19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="16" t="n"/>
+      <c r="N19" s="16" t="inlineStr"/>
+      <c r="O19" s="16" t="n"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Web Application Firewall (WAF)</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="19" t="inlineStr"/>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>As per banks security policy.</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="19" t="n"/>
+      <c r="J20" s="19" t="n"/>
+      <c r="K20" s="19" t="n"/>
+      <c r="L20" s="19" t="n"/>
+      <c r="M20" s="19" t="n"/>
+      <c r="N20" s="19" t="inlineStr"/>
+      <c r="O20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Bastion Host</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="16" t="inlineStr"/>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>As per banks policy.</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>256</v>
+      </c>
+      <c r="J21" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M21" s="16" t="n"/>
+      <c r="N21" s="16" t="inlineStr"/>
+      <c r="O21" s="16" t="n"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Email Service</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Two million mails/month</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="19" t="n"/>
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="19" t="n"/>
+      <c r="L22" s="19" t="n"/>
+      <c r="M22" s="19" t="n"/>
+      <c r="N22" s="19" t="inlineStr"/>
+      <c r="O22" s="19" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="C8:O8"/>
+    <mergeCell ref="C3:O3"/>
+    <mergeCell ref="C17:O17"/>
+    <mergeCell ref="C15:O15"/>
+    <mergeCell ref="C11:O11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>